--- a/data-manipulation-scripts/sheets-cleanup/sheets/VELA 04_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/VELA 04_02.xlsx
@@ -364,7 +364,9 @@
       <c r="C2" s="2">
         <v>2.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -376,7 +378,9 @@
       <c r="C3" s="2">
         <v>2.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -388,7 +392,9 @@
       <c r="C4" s="2">
         <v>20.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -400,7 +406,9 @@
       <c r="C5" s="2">
         <v>57.0</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -412,7 +420,9 @@
       <c r="C6" s="2">
         <v>7.0</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
